--- a/6_patentreports/1_antibiotic_resistance/2_technology_network_output/technology_legend.xlsx
+++ b/6_patentreports/1_antibiotic_resistance/2_technology_network_output/technology_legend.xlsx
@@ -463,53 +463,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Antiinfective Therapy</t>
+          <t>Medical Technology</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A61P  31</t>
+          <t>A61K, A61K   8, A61K  33, A61K  35, A61K  36, A61K  41, A61K  48, A61P   1, A61P  11, A61P  13, A61P  15, A61P  17, A61P  29, A61P  35, A61P  37, A61Q  17, A61Q  19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Antiinfective Therapeutics</t>
+          <t>Medical &amp; Pharmaceutical Technology</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1941</v>
+        <v>2106</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9642857142857142</v>
+        <v>0.9285714285714285</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Medical Technology</t>
+          <t>Antiinfective Therapy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A61K, A61K   8, A61K  33, A61K  35, A61K  36, A61K  41, A61K  48, A61P   1, A61P  11, A61P  15, A61P  17, A61P  29, A61P  35, A61P  37, A61Q  19</t>
+          <t>A61P  31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Medical &amp; Pharmaceutical Technology</t>
+          <t>Antiinfective Therapeutics</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1860</v>
+        <v>2063</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9285714285714285</v>
+        <v>0.9642857142857142</v>
       </c>
     </row>
     <row r="4">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1385</v>
+        <v>1446</v>
       </c>
       <c r="E4" t="n">
         <v>27</v>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>960</v>
+        <v>993</v>
       </c>
       <c r="E5" t="n">
         <v>26</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>812</v>
+        <v>888</v>
       </c>
       <c r="E6" t="n">
         <v>26</v>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>768</v>
+        <v>801</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>709</v>
+        <v>753</v>
       </c>
       <c r="E8" t="n">
         <v>19</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>570</v>
+        <v>602</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="E10" t="n">
         <v>25</v>
@@ -697,53 +697,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chemistry (Heterocyclic)</t>
+          <t>Food Preservation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C07D 401, C07D 403, C07D 417, C07D 471, C07D 487, C07D 501</t>
+          <t>A23K  10, A23K  20, A23L   3, A23L  33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Antibiotic Chemistry - Heterocyclic</t>
+          <t>Food Preservation</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4642857142857142</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Food Preservation</t>
+          <t>Chemistry (Heterocyclic)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A23K  10, A23K  20, A23L   3, A23L  33</t>
+          <t>C07D 401, C07D 403, C07D 417, C07D 471, C07D 487, C07D 501</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Food Preservation</t>
+          <t>Antibiotic Chemistry - Heterocyclic</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.4642857142857142</v>
       </c>
     </row>
     <row r="13">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="E13" t="n">
         <v>23</v>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="E14" t="n">
         <v>22</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="E15" t="n">
         <v>23</v>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E16" t="n">
         <v>23</v>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="E17" t="n">
         <v>23</v>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E18" t="n">
         <v>23</v>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E19" t="n">
         <v>20</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E22" t="n">
         <v>21</v>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E24" t="n">
         <v>20</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E25" t="n">
         <v>15</v>
@@ -1087,53 +1087,53 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Protein Production</t>
+          <t>Organic Chemistry</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C12P  21</t>
+          <t>C07F   5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Protein Production</t>
+          <t>Organic Chemistry</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Organic Chemistry</t>
+          <t>Protein Production</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C07F   5</t>
+          <t>C12P  21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Organic Chemistry</t>
+          <t>Protein Production</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6071428571428571</v>
       </c>
     </row>
     <row r="28">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E29" t="n">
         <v>9</v>
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E30" t="n">
         <v>3</v>
